--- a/templates/mapa_cotacao_modelo.xlsx
+++ b/templates/mapa_cotacao_modelo.xlsx
@@ -1291,7 +1291,7 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="496">
+  <cellXfs count="506">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2921,6 +2921,34 @@
     <xf numFmtId="0" fontId="44" fillId="3" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="41" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="57" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="58" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="58" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="41" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="41" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3463,7 +3491,7 @@
       <c r="A6" s="358" t="n"/>
       <c r="B6" s="382" t="inlineStr">
         <is>
-          <t>Mapa de Cotações</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="C6" s="383" t="inlineStr">
@@ -3708,7 +3736,7 @@
     <row r="12" customFormat="1" s="58" thickBot="1">
       <c r="A12" s="429" t="n"/>
       <c r="B12" s="430" t="n"/>
-      <c r="C12" s="431" t="n"/>
+      <c r="C12" s="496" t="n"/>
       <c r="D12" s="318" t="n"/>
       <c r="E12" s="318" t="n"/>
       <c r="F12" s="318" t="n"/>
@@ -3716,16 +3744,25 @@
       <c r="H12" s="433" t="n"/>
       <c r="I12" s="434" t="n"/>
       <c r="J12" s="435" t="n"/>
-      <c r="K12" s="436" t="n"/>
+      <c r="K12" s="436">
+        <f>H12*J12</f>
+        <v/>
+      </c>
       <c r="L12" s="437" t="n"/>
-      <c r="M12" s="438" t="n"/>
+      <c r="M12" s="438">
+        <f>H12*L12</f>
+        <v/>
+      </c>
       <c r="N12" s="439" t="n"/>
-      <c r="O12" s="440" t="n"/>
+      <c r="O12" s="440">
+        <f>H12*N12</f>
+        <v/>
+      </c>
     </row>
     <row r="13" customFormat="1" s="81">
       <c r="A13" s="441" t="n"/>
       <c r="B13" s="430" t="n"/>
-      <c r="C13" s="431" t="n"/>
+      <c r="C13" s="496" t="n"/>
       <c r="D13" s="318" t="n"/>
       <c r="E13" s="318" t="n"/>
       <c r="F13" s="318" t="n"/>
@@ -3733,16 +3770,25 @@
       <c r="H13" s="433" t="n"/>
       <c r="I13" s="434" t="n"/>
       <c r="J13" s="435" t="n"/>
-      <c r="K13" s="436" t="n"/>
+      <c r="K13" s="436">
+        <f>H13*J13</f>
+        <v/>
+      </c>
       <c r="L13" s="437" t="n"/>
-      <c r="M13" s="438" t="n"/>
+      <c r="M13" s="438">
+        <f>H13*L13</f>
+        <v/>
+      </c>
       <c r="N13" s="439" t="n"/>
-      <c r="O13" s="440" t="n"/>
+      <c r="O13" s="440">
+        <f>H13*N13</f>
+        <v/>
+      </c>
     </row>
     <row r="14" customFormat="1" s="82">
       <c r="A14" s="358" t="n"/>
       <c r="B14" s="430" t="n"/>
-      <c r="C14" s="431" t="n"/>
+      <c r="C14" s="496" t="n"/>
       <c r="D14" s="318" t="n"/>
       <c r="E14" s="318" t="n"/>
       <c r="F14" s="318" t="n"/>
@@ -3750,16 +3796,25 @@
       <c r="H14" s="433" t="n"/>
       <c r="I14" s="434" t="n"/>
       <c r="J14" s="435" t="n"/>
-      <c r="K14" s="436" t="n"/>
+      <c r="K14" s="436">
+        <f>H14*J14</f>
+        <v/>
+      </c>
       <c r="L14" s="437" t="n"/>
-      <c r="M14" s="438" t="n"/>
+      <c r="M14" s="438">
+        <f>H14*L14</f>
+        <v/>
+      </c>
       <c r="N14" s="439" t="n"/>
-      <c r="O14" s="440" t="n"/>
+      <c r="O14" s="440">
+        <f>H14*N14</f>
+        <v/>
+      </c>
     </row>
     <row r="15" customFormat="1" s="48">
       <c r="A15" s="358" t="n"/>
       <c r="B15" s="430" t="n"/>
-      <c r="C15" s="431" t="n"/>
+      <c r="C15" s="496" t="n"/>
       <c r="D15" s="318" t="n"/>
       <c r="E15" s="318" t="n"/>
       <c r="F15" s="318" t="n"/>
@@ -3767,120 +3822,179 @@
       <c r="H15" s="433" t="n"/>
       <c r="I15" s="434" t="n"/>
       <c r="J15" s="435" t="n"/>
-      <c r="K15" s="436" t="n"/>
+      <c r="K15" s="436">
+        <f>H15*J15</f>
+        <v/>
+      </c>
       <c r="L15" s="437" t="n"/>
-      <c r="M15" s="438" t="n"/>
+      <c r="M15" s="438">
+        <f>H15*L15</f>
+        <v/>
+      </c>
       <c r="N15" s="439" t="n"/>
-      <c r="O15" s="440" t="n"/>
+      <c r="O15" s="440">
+        <f>H15*N15</f>
+        <v/>
+      </c>
     </row>
     <row r="16" customFormat="1" s="48">
       <c r="A16" s="358" t="n"/>
-      <c r="B16" s="442" t="n"/>
-      <c r="C16" s="443" t="n"/>
-      <c r="D16" s="443" t="n"/>
-      <c r="E16" s="444" t="n"/>
-      <c r="F16" s="358" t="n"/>
-      <c r="G16" s="358" t="n"/>
-      <c r="H16" s="358" t="n"/>
+      <c r="B16" s="497" t="n"/>
+      <c r="C16" s="498" t="n"/>
+      <c r="D16" s="318" t="n"/>
+      <c r="E16" s="318" t="n"/>
+      <c r="F16" s="318" t="n"/>
+      <c r="G16" s="298" t="n"/>
+      <c r="H16" s="499" t="n"/>
       <c r="I16" s="358" t="n"/>
       <c r="J16" s="445" t="n"/>
-      <c r="K16" s="446" t="n"/>
-      <c r="L16" s="447" t="n"/>
-      <c r="M16" s="448" t="n"/>
+      <c r="K16" s="500">
+        <f>H16*J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="501" t="n"/>
+      <c r="M16" s="502">
+        <f>H16*L16</f>
+        <v/>
+      </c>
       <c r="N16" s="449" t="n"/>
-      <c r="O16" s="450" t="n"/>
+      <c r="O16" s="450">
+        <f>H16*N16</f>
+        <v/>
+      </c>
     </row>
     <row r="17" customFormat="1" s="48">
       <c r="A17" s="358" t="n"/>
-      <c r="B17" s="442" t="n"/>
-      <c r="C17" s="443" t="n"/>
-      <c r="D17" s="443" t="n"/>
-      <c r="E17" s="444" t="n"/>
-      <c r="F17" s="358" t="n"/>
-      <c r="G17" s="358" t="n"/>
-      <c r="H17" s="358" t="n"/>
+      <c r="B17" s="497" t="n"/>
+      <c r="C17" s="498" t="n"/>
+      <c r="D17" s="318" t="n"/>
+      <c r="E17" s="318" t="n"/>
+      <c r="F17" s="318" t="n"/>
+      <c r="G17" s="298" t="n"/>
+      <c r="H17" s="499" t="n"/>
       <c r="I17" s="358" t="n"/>
       <c r="J17" s="445" t="n"/>
-      <c r="K17" s="446" t="n"/>
-      <c r="L17" s="447" t="n"/>
-      <c r="M17" s="448" t="n"/>
+      <c r="K17" s="500">
+        <f>H17*J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="501" t="n"/>
+      <c r="M17" s="502">
+        <f>H17*L17</f>
+        <v/>
+      </c>
       <c r="N17" s="449" t="n"/>
-      <c r="O17" s="450" t="n"/>
+      <c r="O17" s="450">
+        <f>H17*N17</f>
+        <v/>
+      </c>
     </row>
     <row r="18" customFormat="1" s="48">
       <c r="A18" s="358" t="n"/>
-      <c r="B18" s="442" t="n"/>
-      <c r="C18" s="443" t="n"/>
-      <c r="D18" s="451" t="n"/>
-      <c r="E18" s="452" t="n"/>
-      <c r="F18" s="358" t="n"/>
-      <c r="G18" s="358" t="n"/>
-      <c r="H18" s="358" t="n"/>
+      <c r="B18" s="497" t="n"/>
+      <c r="C18" s="498" t="n"/>
+      <c r="D18" s="318" t="n"/>
+      <c r="E18" s="318" t="n"/>
+      <c r="F18" s="318" t="n"/>
+      <c r="G18" s="298" t="n"/>
+      <c r="H18" s="499" t="n"/>
       <c r="I18" s="358" t="n"/>
       <c r="J18" s="445" t="n"/>
-      <c r="K18" s="446" t="n"/>
+      <c r="K18" s="500">
+        <f>H18*J18</f>
+        <v/>
+      </c>
       <c r="L18" s="445" t="n"/>
-      <c r="M18" s="448" t="n"/>
+      <c r="M18" s="502">
+        <f>H18*L18</f>
+        <v/>
+      </c>
       <c r="N18" s="449" t="n"/>
-      <c r="O18" s="450" t="n"/>
+      <c r="O18" s="450">
+        <f>H18*N18</f>
+        <v/>
+      </c>
     </row>
     <row r="19" customFormat="1" s="48">
       <c r="A19" s="358" t="n"/>
-      <c r="B19" s="442" t="n"/>
-      <c r="C19" s="443" t="n"/>
-      <c r="D19" s="451" t="n"/>
-      <c r="E19" s="452" t="n"/>
-      <c r="F19" s="358" t="n"/>
-      <c r="G19" s="358" t="n"/>
-      <c r="H19" s="358" t="n"/>
+      <c r="B19" s="497" t="n"/>
+      <c r="C19" s="498" t="n"/>
+      <c r="D19" s="318" t="n"/>
+      <c r="E19" s="318" t="n"/>
+      <c r="F19" s="318" t="n"/>
+      <c r="G19" s="298" t="n"/>
+      <c r="H19" s="499" t="n"/>
       <c r="I19" s="358" t="n"/>
       <c r="J19" s="445" t="n"/>
-      <c r="K19" s="446" t="n"/>
-      <c r="L19" s="447" t="n"/>
-      <c r="M19" s="448" t="n"/>
+      <c r="K19" s="500">
+        <f>H19*J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="501" t="n"/>
+      <c r="M19" s="502">
+        <f>H19*L19</f>
+        <v/>
+      </c>
       <c r="N19" s="449" t="n"/>
-      <c r="O19" s="450" t="n"/>
+      <c r="O19" s="450">
+        <f>H19*N19</f>
+        <v/>
+      </c>
     </row>
     <row r="20" customFormat="1" s="48">
       <c r="A20" s="358" t="n"/>
-      <c r="B20" s="442" t="n"/>
-      <c r="C20" s="443" t="n"/>
-      <c r="D20" s="451" t="n"/>
-      <c r="E20" s="452" t="n"/>
-      <c r="F20" s="358" t="n"/>
-      <c r="G20" s="358" t="n"/>
-      <c r="H20" s="358" t="n"/>
+      <c r="B20" s="497" t="n"/>
+      <c r="C20" s="498" t="n"/>
+      <c r="D20" s="318" t="n"/>
+      <c r="E20" s="318" t="n"/>
+      <c r="F20" s="318" t="n"/>
+      <c r="G20" s="298" t="n"/>
+      <c r="H20" s="499" t="n"/>
       <c r="I20" s="358" t="n"/>
       <c r="J20" s="445" t="n"/>
-      <c r="K20" s="446" t="n"/>
-      <c r="L20" s="447" t="n"/>
-      <c r="M20" s="448" t="n"/>
+      <c r="K20" s="500">
+        <f>H20*J20</f>
+        <v/>
+      </c>
+      <c r="L20" s="501" t="n"/>
+      <c r="M20" s="502">
+        <f>H20*L20</f>
+        <v/>
+      </c>
       <c r="N20" s="449" t="n"/>
-      <c r="O20" s="450" t="n"/>
+      <c r="O20" s="450">
+        <f>H20*N20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="453" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="454" t="n"/>
-      <c r="C21" s="455" t="n"/>
-      <c r="D21" s="456" t="n"/>
-      <c r="E21" s="457" t="n"/>
-      <c r="F21" s="358" t="n"/>
-      <c r="G21" s="358" t="n"/>
-      <c r="H21" s="358" t="n"/>
+      <c r="A21" s="453" t="n"/>
+      <c r="B21" s="503" t="n"/>
+      <c r="C21" s="504" t="n"/>
+      <c r="D21" s="318" t="n"/>
+      <c r="E21" s="318" t="n"/>
+      <c r="F21" s="318" t="n"/>
+      <c r="G21" s="298" t="n"/>
+      <c r="H21" s="499" t="n"/>
       <c r="I21" s="358" t="n"/>
       <c r="J21" s="458" t="n"/>
-      <c r="K21" s="459" t="n"/>
-      <c r="L21" s="447" t="n"/>
-      <c r="M21" s="448" t="n"/>
+      <c r="K21" s="505">
+        <f>H21*J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="501" t="n"/>
+      <c r="M21" s="502">
+        <f>H21*L21</f>
+        <v/>
+      </c>
       <c r="N21" s="449" t="n"/>
-      <c r="O21" s="450" t="n"/>
+      <c r="O21" s="450">
+        <f>H21*N21</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customFormat="1" customHeight="1" s="50">
-      <c r="A22" s="460" t="n">
-        <v>1</v>
-      </c>
+      <c r="A22" s="460" t="n"/>
       <c r="B22" s="461" t="inlineStr">
         <is>
           <t>Subtotal</t>
@@ -3910,9 +4024,7 @@
       <c r="O22" s="341" t="n"/>
     </row>
     <row r="23" ht="30" customFormat="1" customHeight="1" s="50">
-      <c r="A23" s="460" t="n">
-        <v>1</v>
-      </c>
+      <c r="A23" s="460" t="n"/>
       <c r="B23" s="461" t="inlineStr">
         <is>
           <t>Desconto</t>
@@ -3939,9 +4051,7 @@
       <c r="O23" s="342" t="n"/>
     </row>
     <row r="24" ht="30" customFormat="1" customHeight="1" s="50">
-      <c r="A24" s="460" t="n">
-        <v>1</v>
-      </c>
+      <c r="A24" s="460" t="n"/>
       <c r="B24" s="461" t="inlineStr">
         <is>
           <t>Frete</t>
@@ -3963,9 +4073,7 @@
       <c r="P24" s="345" t="n"/>
     </row>
     <row r="25" ht="30" customFormat="1" customHeight="1" s="50" thickBot="1">
-      <c r="A25" s="460" t="n">
-        <v>1</v>
-      </c>
+      <c r="A25" s="460" t="n"/>
       <c r="B25" s="466" t="inlineStr">
         <is>
           <t>Total Geral</t>
@@ -3996,9 +4104,7 @@
       <c r="P25" s="52" t="n"/>
     </row>
     <row r="26" ht="30" customFormat="1" customHeight="1" s="50">
-      <c r="A26" s="460" t="n">
-        <v>1</v>
-      </c>
+      <c r="A26" s="460" t="n"/>
       <c r="B26" s="470" t="inlineStr">
         <is>
           <t>Condições de Entrega</t>
@@ -4019,9 +4125,7 @@
       <c r="O26" s="292" t="n"/>
     </row>
     <row r="27" ht="30" customFormat="1" customHeight="1" s="50" thickBot="1">
-      <c r="A27" s="460" t="n">
-        <v>1</v>
-      </c>
+      <c r="A27" s="460" t="n"/>
       <c r="B27" s="473" t="inlineStr">
         <is>
           <t>Condições de Pagamento</t>
@@ -4054,9 +4158,7 @@
       <c r="O27" s="298" t="n"/>
     </row>
     <row r="28" ht="19.9" customFormat="1" customHeight="1" s="33">
-      <c r="A28" s="477" t="n">
-        <v>1</v>
-      </c>
+      <c r="A28" s="477" t="n"/>
       <c r="B28" s="478" t="inlineStr">
         <is>
           <t>Observação:</t>
@@ -4089,9 +4191,7 @@
       <c r="O28" s="280" t="n"/>
     </row>
     <row r="29" ht="19.9" customFormat="1" customHeight="1" s="33">
-      <c r="A29" s="477" t="n">
-        <v>1</v>
-      </c>
+      <c r="A29" s="477" t="n"/>
       <c r="B29" s="483" t="n"/>
       <c r="C29" s="484" t="n"/>
       <c r="D29" s="484" t="n"/>
@@ -4108,9 +4208,7 @@
       <c r="O29" s="285" t="n"/>
     </row>
     <row r="30" ht="19.9" customFormat="1" customHeight="1" s="33">
-      <c r="A30" s="477" t="n">
-        <v>1</v>
-      </c>
+      <c r="A30" s="477" t="n"/>
       <c r="B30" s="483" t="n"/>
       <c r="C30" s="484" t="n"/>
       <c r="D30" s="484" t="n"/>
@@ -4127,9 +4225,7 @@
       <c r="O30" s="285" t="n"/>
     </row>
     <row r="31" ht="19.9" customFormat="1" customHeight="1" s="33">
-      <c r="A31" s="477" t="n">
-        <v>1</v>
-      </c>
+      <c r="A31" s="477" t="n"/>
       <c r="B31" s="483" t="n"/>
       <c r="C31" s="484" t="n"/>
       <c r="D31" s="484" t="n"/>
@@ -4146,9 +4242,7 @@
       <c r="O31" s="285" t="n"/>
     </row>
     <row r="32" ht="19.9" customFormat="1" customHeight="1" s="33">
-      <c r="A32" s="477" t="n">
-        <v>1</v>
-      </c>
+      <c r="A32" s="477" t="n"/>
       <c r="B32" s="483" t="n"/>
       <c r="C32" s="484" t="n"/>
       <c r="D32" s="484" t="n"/>
@@ -4165,9 +4259,7 @@
       <c r="O32" s="285" t="n"/>
     </row>
     <row r="33" ht="19.9" customFormat="1" customHeight="1" s="33" thickBot="1">
-      <c r="A33" s="477" t="n">
-        <v>1</v>
-      </c>
+      <c r="A33" s="477" t="n"/>
       <c r="B33" s="488" t="n"/>
       <c r="C33" s="489" t="n"/>
       <c r="D33" s="489" t="n"/>
@@ -4241,7 +4333,7 @@
     <filterColumn colId="6" hiddenButton="0" showButton="0"/>
     <filterColumn colId="7" hiddenButton="0" showButton="0"/>
   </autoFilter>
-  <mergeCells count="66">
+  <mergeCells count="72">
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="L7:M7"/>
@@ -4258,8 +4350,10 @@
     <mergeCell ref="N22:O22"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="J24:K24"/>
+    <mergeCell ref="C16:G16"/>
     <mergeCell ref="L24:M24"/>
     <mergeCell ref="N28:O33"/>
     <mergeCell ref="E8:G9"/>
@@ -4277,6 +4371,7 @@
     <mergeCell ref="N23:O23"/>
     <mergeCell ref="E2:N3"/>
     <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C21:G21"/>
     <mergeCell ref="B2:D5"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="E4:H4"/>
@@ -4292,6 +4387,7 @@
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="L9:M9"/>
+    <mergeCell ref="C17:G17"/>
     <mergeCell ref="I4:M4"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="C7:D7"/>
@@ -4301,12 +4397,14 @@
     <mergeCell ref="N24:O24"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="E30:H30"/>
+    <mergeCell ref="C19:G19"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="J28:K33"/>
     <mergeCell ref="J23:K23"/>
     <mergeCell ref="L28:M33"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C18:G18"/>
     <mergeCell ref="B26:I26"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">

--- a/templates/mapa_cotacao_modelo.xlsx
+++ b/templates/mapa_cotacao_modelo.xlsx
@@ -3500,16 +3500,8 @@
         </is>
       </c>
       <c r="D6" s="285" t="n"/>
-      <c r="E6" s="384" t="inlineStr">
-        <is>
-          <t>Data:</t>
-        </is>
-      </c>
-      <c r="F6" s="386" t="inlineStr">
-        <is>
-          <t>[DATA]</t>
-        </is>
-      </c>
+      <c r="E6" s="384" t="n"/>
+      <c r="F6" s="386" t="n"/>
       <c r="G6" s="386" t="inlineStr">
         <is>
           <t>Comprador:</t>
@@ -3562,11 +3554,7 @@
           <t>C.C.:</t>
         </is>
       </c>
-      <c r="F7" s="393" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obra: </t>
-        </is>
-      </c>
+      <c r="F7" s="393" t="n"/>
       <c r="G7" s="298" t="n"/>
       <c r="H7" s="395" t="inlineStr">
         <is>
@@ -3598,13 +3586,7 @@
         </is>
       </c>
       <c r="D8" s="285" t="n"/>
-      <c r="E8" s="401" t="inlineStr">
-        <is>
-          <t>[Nome da Obra]</t>
-        </is>
-      </c>
-      <c r="F8" s="303" t="n"/>
-      <c r="G8" s="304" t="n"/>
+      <c r="E8" s="401" t="n"/>
       <c r="H8" s="495" t="inlineStr">
         <is>
           <t>Bruno Felizardo</t>
@@ -3635,9 +3617,6 @@
         </is>
       </c>
       <c r="D9" s="288" t="n"/>
-      <c r="E9" s="307" t="n"/>
-      <c r="F9" s="308" t="n"/>
-      <c r="G9" s="309" t="n"/>
       <c r="H9" s="412" t="n"/>
       <c r="I9" s="413" t="inlineStr">
         <is>
@@ -4333,7 +4312,7 @@
     <filterColumn colId="6" hiddenButton="0" showButton="0"/>
     <filterColumn colId="7" hiddenButton="0" showButton="0"/>
   </autoFilter>
-  <mergeCells count="72">
+  <mergeCells count="71">
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="L7:M7"/>
@@ -4356,7 +4335,6 @@
     <mergeCell ref="C16:G16"/>
     <mergeCell ref="L24:M24"/>
     <mergeCell ref="N28:O33"/>
-    <mergeCell ref="E8:G9"/>
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="J27:K27"/>

--- a/templates/mapa_cotacao_modelo.xlsx
+++ b/templates/mapa_cotacao_modelo.xlsx
@@ -494,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="64">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1276,6 +1276,42 @@
         <color indexed="64"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="11">
@@ -1291,7 +1327,7 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="506">
+  <cellXfs count="510">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2950,6 +2986,14 @@
     <xf numFmtId="166" fontId="41" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="64" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3352,7 +3396,7 @@
   <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="21"/>
   <cols>
-    <col width="3" customWidth="1" style="2" min="1" max="1"/>
+    <col hidden="1" width="0.5" customWidth="1" style="2" min="1" max="1"/>
     <col width="20.28515625" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
     <col width="8.42578125" customWidth="1" style="2" min="3" max="3"/>
     <col width="14" customWidth="1" style="2" min="4" max="4"/>
@@ -3366,7 +3410,7 @@
     <col width="9.140625" customWidth="1" style="2" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" thickBot="1">
+    <row r="1" hidden="1" ht="1" customHeight="1" thickBot="1">
       <c r="A1" s="358" t="n"/>
       <c r="B1" s="359" t="n"/>
       <c r="C1" s="359" t="n"/>
@@ -3485,7 +3529,7 @@
           <t>Cotação 03</t>
         </is>
       </c>
-      <c r="O5" s="294" t="n"/>
+      <c r="O5" s="506" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="358" t="n"/>
@@ -3652,12 +3696,8 @@
       <c r="O10" s="312" t="n"/>
     </row>
     <row r="11" customFormat="1" s="19" thickBot="1">
-      <c r="A11" s="422" t="inlineStr">
-        <is>
-          <t>Item orçado</t>
-        </is>
-      </c>
-      <c r="B11" s="423" t="inlineStr">
+      <c r="A11" s="422" t="n"/>
+      <c r="B11" s="507" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
@@ -3824,8 +3864,8 @@
       <c r="E16" s="318" t="n"/>
       <c r="F16" s="318" t="n"/>
       <c r="G16" s="298" t="n"/>
-      <c r="H16" s="499" t="n"/>
-      <c r="I16" s="358" t="n"/>
+      <c r="H16" s="433" t="n"/>
+      <c r="I16" s="398" t="n"/>
       <c r="J16" s="445" t="n"/>
       <c r="K16" s="500">
         <f>H16*J16</f>
@@ -3850,8 +3890,8 @@
       <c r="E17" s="318" t="n"/>
       <c r="F17" s="318" t="n"/>
       <c r="G17" s="298" t="n"/>
-      <c r="H17" s="499" t="n"/>
-      <c r="I17" s="358" t="n"/>
+      <c r="H17" s="433" t="n"/>
+      <c r="I17" s="398" t="n"/>
       <c r="J17" s="445" t="n"/>
       <c r="K17" s="500">
         <f>H17*J17</f>
@@ -3876,8 +3916,8 @@
       <c r="E18" s="318" t="n"/>
       <c r="F18" s="318" t="n"/>
       <c r="G18" s="298" t="n"/>
-      <c r="H18" s="499" t="n"/>
-      <c r="I18" s="358" t="n"/>
+      <c r="H18" s="433" t="n"/>
+      <c r="I18" s="398" t="n"/>
       <c r="J18" s="445" t="n"/>
       <c r="K18" s="500">
         <f>H18*J18</f>
@@ -3902,8 +3942,8 @@
       <c r="E19" s="318" t="n"/>
       <c r="F19" s="318" t="n"/>
       <c r="G19" s="298" t="n"/>
-      <c r="H19" s="499" t="n"/>
-      <c r="I19" s="358" t="n"/>
+      <c r="H19" s="433" t="n"/>
+      <c r="I19" s="398" t="n"/>
       <c r="J19" s="445" t="n"/>
       <c r="K19" s="500">
         <f>H19*J19</f>
@@ -3928,8 +3968,8 @@
       <c r="E20" s="318" t="n"/>
       <c r="F20" s="318" t="n"/>
       <c r="G20" s="298" t="n"/>
-      <c r="H20" s="499" t="n"/>
-      <c r="I20" s="358" t="n"/>
+      <c r="H20" s="433" t="n"/>
+      <c r="I20" s="398" t="n"/>
       <c r="J20" s="445" t="n"/>
       <c r="K20" s="500">
         <f>H20*J20</f>
@@ -3954,8 +3994,8 @@
       <c r="E21" s="318" t="n"/>
       <c r="F21" s="318" t="n"/>
       <c r="G21" s="298" t="n"/>
-      <c r="H21" s="499" t="n"/>
-      <c r="I21" s="358" t="n"/>
+      <c r="H21" s="433" t="n"/>
+      <c r="I21" s="398" t="n"/>
       <c r="J21" s="458" t="n"/>
       <c r="K21" s="505">
         <f>H21*J21</f>
@@ -4000,7 +4040,7 @@
         <f>SUM(O12:O21)</f>
         <v/>
       </c>
-      <c r="O22" s="341" t="n"/>
+      <c r="O22" s="508" t="n"/>
     </row>
     <row r="23" ht="30" customFormat="1" customHeight="1" s="50">
       <c r="A23" s="460" t="n"/>
@@ -4134,7 +4174,7 @@
           <t>Vide observações abaixo.</t>
         </is>
       </c>
-      <c r="O27" s="298" t="n"/>
+      <c r="O27" s="509" t="n"/>
     </row>
     <row r="28" ht="19.9" customFormat="1" customHeight="1" s="33">
       <c r="A28" s="477" t="n"/>

--- a/templates/mapa_cotacao_modelo.xlsx
+++ b/templates/mapa_cotacao_modelo.xlsx
@@ -1327,7 +1327,7 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="510">
+  <cellXfs count="511">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2994,6 +2994,10 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3482,7 +3486,7 @@
       <c r="F4" s="291" t="n"/>
       <c r="G4" s="291" t="n"/>
       <c r="H4" s="292" t="n"/>
-      <c r="I4" s="375" t="inlineStr">
+      <c r="I4" s="510" t="inlineStr">
         <is>
           <t>FORNECEDORES</t>
         </is>
@@ -3491,8 +3495,8 @@
       <c r="K4" s="287" t="n"/>
       <c r="L4" s="287" t="n"/>
       <c r="M4" s="287" t="n"/>
-      <c r="N4" s="376" t="n"/>
-      <c r="O4" s="377" t="n"/>
+      <c r="N4" s="287" t="n"/>
+      <c r="O4" s="288" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" thickBot="1">
       <c r="A5" s="358" t="n"/>
@@ -3529,7 +3533,7 @@
           <t>Cotação 03</t>
         </is>
       </c>
-      <c r="O5" s="506" t="n"/>
+      <c r="O5" s="294" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="358" t="n"/>
@@ -3544,8 +3548,16 @@
         </is>
       </c>
       <c r="D6" s="285" t="n"/>
-      <c r="E6" s="384" t="n"/>
-      <c r="F6" s="386" t="n"/>
+      <c r="E6" s="384" t="inlineStr">
+        <is>
+          <t>Data:</t>
+        </is>
+      </c>
+      <c r="F6" s="386" t="inlineStr">
+        <is>
+          <t>[DATA]</t>
+        </is>
+      </c>
       <c r="G6" s="386" t="inlineStr">
         <is>
           <t>Comprador:</t>
@@ -3598,7 +3610,11 @@
           <t>C.C.:</t>
         </is>
       </c>
-      <c r="F7" s="393" t="n"/>
+      <c r="F7" s="393" t="inlineStr">
+        <is>
+          <t>Obra:</t>
+        </is>
+      </c>
       <c r="G7" s="298" t="n"/>
       <c r="H7" s="395" t="inlineStr">
         <is>
@@ -3630,7 +3646,13 @@
         </is>
       </c>
       <c r="D8" s="285" t="n"/>
-      <c r="E8" s="401" t="n"/>
+      <c r="E8" s="401" t="inlineStr">
+        <is>
+          <t>[Endereço completo da Obra]</t>
+        </is>
+      </c>
+      <c r="F8" s="303" t="n"/>
+      <c r="G8" s="304" t="n"/>
       <c r="H8" s="495" t="inlineStr">
         <is>
           <t>Bruno Felizardo</t>
@@ -3661,6 +3683,9 @@
         </is>
       </c>
       <c r="D9" s="288" t="n"/>
+      <c r="E9" s="307" t="n"/>
+      <c r="F9" s="308" t="n"/>
+      <c r="G9" s="309" t="n"/>
       <c r="H9" s="412" t="n"/>
       <c r="I9" s="413" t="inlineStr">
         <is>
@@ -4036,11 +4061,11 @@
         <v/>
       </c>
       <c r="M22" s="341" t="n"/>
-      <c r="N22" s="464">
+      <c r="N22" s="465">
         <f>SUM(O12:O21)</f>
         <v/>
       </c>
-      <c r="O22" s="508" t="n"/>
+      <c r="O22" s="342" t="n"/>
     </row>
     <row r="23" ht="30" customFormat="1" customHeight="1" s="50">
       <c r="A23" s="460" t="n"/>
@@ -4174,7 +4199,7 @@
           <t>Vide observações abaixo.</t>
         </is>
       </c>
-      <c r="O27" s="509" t="n"/>
+      <c r="O27" s="298" t="n"/>
     </row>
     <row r="28" ht="19.9" customFormat="1" customHeight="1" s="33">
       <c r="A28" s="477" t="n"/>
@@ -4352,7 +4377,7 @@
     <filterColumn colId="6" hiddenButton="0" showButton="0"/>
     <filterColumn colId="7" hiddenButton="0" showButton="0"/>
   </autoFilter>
-  <mergeCells count="71">
+  <mergeCells count="72">
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="L7:M7"/>
@@ -4363,6 +4388,7 @@
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="B22:I22"/>
+    <mergeCell ref="I4:O4"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="E32:H32"/>
@@ -4375,6 +4401,7 @@
     <mergeCell ref="C16:G16"/>
     <mergeCell ref="L24:M24"/>
     <mergeCell ref="N28:O33"/>
+    <mergeCell ref="E8:G9"/>
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="J27:K27"/>
@@ -4406,7 +4433,6 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="C17:G17"/>
-    <mergeCell ref="I4:M4"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E31:H31"/>
